--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N3_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.09853531583701</v>
+        <v>12.85351198882351</v>
       </c>
       <c r="D2" t="n">
-        <v>78.93745036024603</v>
+        <v>12.82733568353998</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
